--- a/OGE_progress_tracker.xlsx
+++ b/OGE_progress_tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Трекер" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Трекер" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Трекер'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Трекер'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Трекер'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -221,6 +221,36 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="342900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -724,5 +754,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>